--- a/XLibur.Tests/Resource/Examples/Tables/UsingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/UsingTables.xlsx
@@ -763,13 +763,13 @@
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.567768" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="6.567768" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.853482" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.139196" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="3.710625" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="13.853482" style="0" customWidth="1"/>
   </x:cols>

--- a/XLibur.Tests/Resource/Examples/Tables/UsingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/UsingTables.xlsx
@@ -818,6 +818,7 @@
       </x:c>
       <x:c r="G3" s="17">
         <x:f>(DATE(2017, 10, 3) - E3) / 365</x:f>
+        <x:v>98.7671232876712</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
         <x:v>0</x:v>
@@ -844,6 +845,7 @@
       </x:c>
       <x:c r="G4" s="17">
         <x:f>(DATE(2017, 10, 3) - E4) / 365</x:f>
+        <x:v>110.660273972603</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
         <x:v>1</x:v>
@@ -870,6 +872,7 @@
       </x:c>
       <x:c r="G5" s="17">
         <x:f>(DATE(2017, 10, 3) - E5) / 365</x:f>
+        <x:v>95.8657534246575</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>2</x:v>
@@ -904,7 +907,7 @@
       </x:c>
     </x:row>
     <x:row r="9" spans="1:11">
-      <x:c r="I9" s="0">
+      <x:c r="I9" s="0" t="str">
         <x:f>CONCATENATE("Count: ", CountA(Headers[Table Headers]))</x:f>
       </x:c>
     </x:row>
